--- a/assets/constructions/examples/ctd_mih_single.xlsx
+++ b/assets/constructions/examples/ctd_mih_single.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:AG6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -574,158 +574,186 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BF-12.5R-M12-1T</t>
+          <t>M270BD016M08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DEREK</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BF</t>
+          <t>M270</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>12.5</v>
+        <v>8.5</v>
       </c>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>47</v>
+      </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>53000</v>
+      </c>
       <c r="N2" t="n">
-        <v>0.14</v>
+        <v>0.05</v>
       </c>
       <c r="O2" t="n">
-        <v>12.5</v>
+        <v>8</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>P3202-D25</t>
+          <t>M270B.16</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>METRIC_THREAD:M12</t>
+          <t>METRIC_THREAD:M8</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>DER_P3202-D25</t>
+          <t>WIDIA_M2B16H</t>
         </is>
       </c>
       <c r="V2" t="n">
         <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>M12</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>P32*_H</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr"/>
+          <t>WID_M2B16_H</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>WID_M270BD_1185</t>
+        </is>
+      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2019 / DEREK</t>
-        </is>
-      </c>
+          <t>2017 / WIDIA основной каталог EN</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M270TD012M08</t>
+          <t>BF-8R-M8-1T</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>M270</t>
+          <t>BF</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E3" t="n">
         <v>8.5</v>
       </c>
-      <c r="F3" t="n">
-        <v>13</v>
-      </c>
-      <c r="G3" t="n">
-        <v>42</v>
-      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="n">
-        <v>55000</v>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="O3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>M270TF12R..</t>
+          <t>P3202-D16</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -737,14 +765,14 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>WIDIA_M2F12H</t>
+          <t>DER_P3202-D16</t>
         </is>
       </c>
       <c r="V3" t="n">
         <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -752,29 +780,39 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>WID_M2F12_H</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>WID_M270TD_1207</t>
-        </is>
-      </c>
+          <t>P32*_H</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2017 / WIDIA основной каталог EN</t>
-        </is>
+          <t>2019 / DEREK</t>
+        </is>
+      </c>
+      <c r="AD3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>64.92</v>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>5321.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>012R62090-02-UM06030</t>
+          <t>010R62090-02-UM06030</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -782,13 +820,9 @@
           <t>PALBIT</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>W-PRO 62090</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
         <v>6.5</v>
@@ -808,16 +842,12 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>0.016</v>
+        <v>0.011</v>
       </c>
       <c r="O4" t="n">
-        <v>6</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>WCR 12…/WCL 12…</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
@@ -834,7 +864,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>PALB_WC16H</t>
+          <t>PALB_WC10H</t>
         </is>
       </c>
       <c r="V4" t="n">
@@ -857,11 +887,25 @@
           <t>2022/PALBIT Главный каталог</t>
         </is>
       </c>
+      <c r="AD4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>173.34</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>15935.79</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M270TD016M08</t>
+          <t>M270BD020M10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -875,20 +919,18 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E5" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="F5" t="n">
-        <v>13</v>
-      </c>
+        <v>10.5</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J5" t="n">
         <v>2</v>
@@ -898,17 +940,17 @@
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>53000</v>
+        <v>52000</v>
       </c>
       <c r="N5" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="O5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>M270TF16R..</t>
+          <t>M270B.20</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -922,12 +964,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>METRIC_THREAD:M8</t>
+          <t>METRIC_THREAD:M10</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>WIDIA_M2F16H</t>
+          <t>WIDIA_M2B20H</t>
         </is>
       </c>
       <c r="V5" t="n">
@@ -938,21 +980,21 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>M10</t>
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>WID_M2F16_H</t>
+          <t>WID_M2B20_H</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>WID_M270TD_1215</t>
+          <t>WID_M270BD_1189</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -960,31 +1002,45 @@
           <t>2017 / WIDIA основной каталог EN</t>
         </is>
       </c>
+      <c r="AD5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>010R62090-02-UM06030</t>
+          <t>M270TD016M08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PALBIT</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>WIDIA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>M270</t>
+        </is>
+      </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
+        <v>8.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>13</v>
+      </c>
       <c r="G6" t="n">
+        <v>47</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="n">
         <v>30</v>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
         <v>2</v>
       </c>
@@ -992,31 +1048,37 @@
         <v>1</v>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>53000</v>
+      </c>
       <c r="N6" t="n">
-        <v>0.011</v>
+        <v>0.09</v>
       </c>
       <c r="O6" t="n">
-        <v>5</v>
-      </c>
-      <c r="P6" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>M270TF16R..</t>
+        </is>
+      </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>METRIC_THREAD:M6</t>
+          <t>METRIC_THREAD:M8</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>PALB_WC10H</t>
+          <t>WIDIA_M2F16H</t>
         </is>
       </c>
       <c r="V6" t="n">
@@ -1027,18 +1089,34 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>M6</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr"/>
+          <t>M8</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>10</v>
+      </c>
       <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>WID_M2F16_H</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>WID_M270TD_1215</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2022/PALBIT Главный каталог</t>
-        </is>
-      </c>
+          <t>2017 / WIDIA основной каталог EN</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
